--- a/files/UAE_006_ФФЗ.xlsx
+++ b/files/UAE_006_ФФЗ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zinov\OneDrive\Desktop\РАБОЧАЯ\001 ИМПОРТ\001 containers\2026\001 UAE\UAE#6_STPARTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1949A40A-EAF3-4487-B15B-C4B06D0A5943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5D7D37E-A7F1-466A-93CD-8B869A657632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="2040" windowWidth="35295" windowHeight="18060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ФПЗ_Э6" sheetId="1" r:id="rId1"/>
